--- a/importer-files/Chotu_Products_Import_Template_Discount_Tags.xlsx
+++ b/importer-files/Chotu_Products_Import_Template_Discount_Tags.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="READ ME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Brand Info" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Products" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Product Images" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Option Groups" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Options" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Enrichment Notes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Variant Combinations" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Variant Mapping Guide" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Importer Instructions" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Importer Column Guide" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="READ ME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand Info" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Images" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Option Groups" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Options" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enrichment Notes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variant Combinations" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variant Mapping Guide" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importer Instructions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importer Column Guide" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -1683,7 +1683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:AA1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1711,6 +1711,7 @@
     <col width="28" customWidth="1" min="24" max="24"/>
     <col width="28" customWidth="1" min="25" max="25"/>
     <col width="28" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1842,6 +1843,11 @@
       <c r="Z1" s="4" t="inlineStr">
         <is>
           <t>source_discount_tag</t>
+        </is>
+      </c>
+      <c r="AA1" s="4" t="inlineStr">
+        <is>
+          <t>stock_quantity (kitni quantity bechni hai)</t>
         </is>
       </c>
     </row>

--- a/importer-files/Chotu_Products_Import_Template_Discount_Tags.xlsx
+++ b/importer-files/Chotu_Products_Import_Template_Discount_Tags.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variant Mapping Guide" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importer Instructions" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importer Column Guide" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ranking Guide" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -129,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -185,6 +186,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -290,6 +294,31 @@
     <comment ref="Z1" authorId="0" shapeId="0">
       <text>
         <t>Exact website badge text only when independently verified. Blank means not fetched.</t>
+      </text>
+    </comment>
+    <comment ref="AB1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional positive integer; lower numbers appear first. Store-specific category merchandising priority, not a sales claim. Use the same value for every product in that category within a shop. Blank means unassigned.</t>
+      </text>
+    </comment>
+    <comment ref="AC1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional positive integer; lower numbers appear first within the category. Set only from documented evidence or explicit manual selection. Blank means unranked.</t>
+      </text>
+    </comment>
+    <comment ref="AD1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional: store_bestseller, external_trend, or manual_selection. External popularity is not proof of this shop’s sales. Blank means no ranking evidence recorded.</t>
+      </text>
+    </comment>
+    <comment ref="AE1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence page URL. Required for store_bestseller and external_trend; do not substitute the product URL unless it actually documents the ranking.</t>
+      </text>
+    </comment>
+    <comment ref="AF1" authorId="0" shapeId="0">
+      <text>
+        <t>Date/time when the evidence was actually checked, preferably ISO 8601 with timezone. Leave blank until checked; do not invent freshness.</t>
       </text>
     </comment>
   </commentList>
@@ -539,12 +568,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B41"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -559,6 +589,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -580,6 +611,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -615,6 +647,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -643,6 +676,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -664,6 +698,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -678,6 +713,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -692,6 +728,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -720,6 +757,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="B35" s="2" t="inlineStr">
         <is>
@@ -727,6 +765,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -1297,6 +1336,160 @@
         </is>
       </c>
       <c r="D15" s="30" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="31" t="n"/>
+      <c r="B1" s="31" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>Field / Topic</t>
+        </is>
+      </c>
+      <c r="B2" s="31" t="inlineStr">
+        <is>
+          <t>Importer and storefront contract</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>category_priority</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>Optional positive integer; lower numbers appear first. Store-specific category merchandising priority, not a sales claim. Use the same value for every product in that category within a shop. Blank means unassigned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>product_priority</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>Optional positive integer; lower numbers appear first within the category. Set only from documented evidence or explicit manual selection. Blank means unranked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>popularity_basis</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Optional: store_bestseller, external_trend, or manual_selection. External popularity is not proof of this shop’s sales. Blank means no ranking evidence recorded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>popularity_source_url</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>Evidence page URL. Required for store_bestseller and external_trend; do not substitute the product URL unless it actually documents the ranking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>popularity_checked_at</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>Date/time when the evidence was actually checked, preferably ISO 8601 with timezone. Leave blank until checked; do not invent freshness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>Default display order</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>Within the shop: category_priority ascending, with blank priorities last; ties preserve existing category order. Within each category: product_priority ascending, blanks last; then valid payable product price ascending; equal prices: genuine discount descending, then original import order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>Evidence validation</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>Reject unsupported basis values. Require an actual evidence URL and checked timestamp for store_bestseller/external_trend. Do not generate a best-selling badge from external_trend or manual_selection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>Category consistency</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>Validate one consistent category_priority per shop/category. Do not let alphabetical category ordering put unrelated side categories ahead of the shop’s primary categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>All ranking fields are optional. Preserve blank values as null. Existing product, stock, price, shop_code, variants and image columns retain their existing meaning. Column matching must use header names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>These columns store ranking evidence and priorities. Template updates alone do not collect bestseller evidence, change an active cloud worker, or update the website importer/storefront.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1683,7 +1876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1712,6 +1905,11 @@
     <col width="28" customWidth="1" min="25" max="25"/>
     <col width="28" customWidth="1" min="26" max="26"/>
     <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="25" customWidth="1" min="28" max="28"/>
+    <col width="25" customWidth="1" min="29" max="29"/>
+    <col width="25" customWidth="1" min="30" max="30"/>
+    <col width="55" customWidth="1" min="31" max="31"/>
+    <col width="25" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1848,6 +2046,31 @@
       <c r="AA1" s="4" t="inlineStr">
         <is>
           <t>stock_quantity (kitni quantity bechni hai)</t>
+        </is>
+      </c>
+      <c r="AB1" s="4" t="inlineStr">
+        <is>
+          <t>category_priority</t>
+        </is>
+      </c>
+      <c r="AC1" s="4" t="inlineStr">
+        <is>
+          <t>product_priority</t>
+        </is>
+      </c>
+      <c r="AD1" s="4" t="inlineStr">
+        <is>
+          <t>popularity_basis</t>
+        </is>
+      </c>
+      <c r="AE1" s="4" t="inlineStr">
+        <is>
+          <t>popularity_source_url</t>
+        </is>
+      </c>
+      <c r="AF1" s="4" t="inlineStr">
+        <is>
+          <t>popularity_checked_at</t>
         </is>
       </c>
     </row>
@@ -1857,7 +2080,7 @@
       <formula>AND($A2&lt;&gt;"",COUNTIF($A$2:$A$5000,$A2)&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="7">
     <dataValidation sqref="I2:I5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Galat value" error="Sirf new ya used likhein" type="list">
       <formula1>"new,used"</formula1>
     </dataValidation>
@@ -1869,6 +2092,15 @@
     </dataValidation>
     <dataValidation sqref="J2:J5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Galat value" error="Warranty mahine ka number ho" type="whole" operator="greaterThanOrEqual">
       <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="AB2:AB1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid priority" error="Use a positive whole number or leave blank." type="whole" operator="greaterThanOrEqual">
+      <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation sqref="AC2:AC1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid priority" error="Use a positive whole number or leave blank." type="whole" operator="greaterThanOrEqual">
+      <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation sqref="AD2:AD1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"store_bestseller,external_trend,manual_selection"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/importer-files/Chotu_Products_Import_Template_Discount_Tags.xlsx
+++ b/importer-files/Chotu_Products_Import_Template_Discount_Tags.xlsx
@@ -321,6 +321,11 @@
         <t>Date/time when the evidence was actually checked, preferably ISO 8601 with timezone. Leave blank until checked; do not invent freshness.</t>
       </text>
     </comment>
+    <comment ref="AG1" authorId="0" shapeId="0">
+      <text>
+        <t>Internal Rule 804 research note: record observed bestseller-sort position, product-page merchant labels, named collection membership, source URLs, check times and uncertainty. Top/featured collection names alone do not prove sales. Preserve as plain text; do not display automatically as customer product description.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -1348,7 +1353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1488,6 +1493,18 @@
       <c r="B12" s="31" t="inlineStr">
         <is>
           <t>These columns store ranking evidence and priorities. Template updates alone do not collect bestseller evidence, change an active cloud worker, or update the website importer/storefront.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>analysis_note</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Internal Rule 804 research note: record observed bestseller-sort position, product-page merchant labels, named collection membership, source URLs, check times and uncertainty. Top/featured collection names alone do not prove sales. Preserve as plain text; do not display automatically as customer product description.</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1910,6 +1927,7 @@
     <col width="25" customWidth="1" min="30" max="30"/>
     <col width="55" customWidth="1" min="31" max="31"/>
     <col width="25" customWidth="1" min="32" max="32"/>
+    <col width="80" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2071,6 +2089,11 @@
       <c r="AF1" s="4" t="inlineStr">
         <is>
           <t>popularity_checked_at</t>
+        </is>
+      </c>
+      <c r="AG1" s="4" t="inlineStr">
+        <is>
+          <t>analysis_note</t>
         </is>
       </c>
     </row>

--- a/importer-files/Chotu_Products_Import_Template_Discount_Tags.xlsx
+++ b/importer-files/Chotu_Products_Import_Template_Discount_Tags.xlsx
@@ -1893,7 +1893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AM1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2094,6 +2094,36 @@
       <c r="AG1" s="4" t="inlineStr">
         <is>
           <t>analysis_note</t>
+        </is>
+      </c>
+      <c r="AH1" s="4" t="inlineStr">
+        <is>
+          <t>website_category_order</t>
+        </is>
+      </c>
+      <c r="AI1" s="4" t="inlineStr">
+        <is>
+          <t>website_subcategory_order</t>
+        </is>
+      </c>
+      <c r="AJ1" s="4" t="inlineStr">
+        <is>
+          <t>website_product_order</t>
+        </is>
+      </c>
+      <c r="AK1" s="4" t="inlineStr">
+        <is>
+          <t>website_order_source_url</t>
+        </is>
+      </c>
+      <c r="AL1" s="4" t="inlineStr">
+        <is>
+          <t>website_order_checked_at</t>
+        </is>
+      </c>
+      <c r="AM1" s="4" t="inlineStr">
+        <is>
+          <t>website_order_status</t>
         </is>
       </c>
     </row>

--- a/importer-files/Chotu_Products_Import_Template_Discount_Tags.xlsx
+++ b/importer-files/Chotu_Products_Import_Template_Discount_Tags.xlsx
@@ -1893,7 +1893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM1"/>
+  <dimension ref="A1:AQ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2124,6 +2124,26 @@
       <c r="AM1" s="4" t="inlineStr">
         <is>
           <t>website_order_status</t>
+        </is>
+      </c>
+      <c r="AN1" s="4" t="inlineStr">
+        <is>
+          <t>website_category_path</t>
+        </is>
+      </c>
+      <c r="AO1" s="4" t="inlineStr">
+        <is>
+          <t>website_category_source_url</t>
+        </is>
+      </c>
+      <c r="AP1" s="4" t="inlineStr">
+        <is>
+          <t>website_category_checked_at</t>
+        </is>
+      </c>
+      <c r="AQ1" s="4" t="inlineStr">
+        <is>
+          <t>website_category_status</t>
         </is>
       </c>
     </row>

--- a/importer-files/Chotu_Products_Import_Template_Discount_Tags.xlsx
+++ b/importer-files/Chotu_Products_Import_Template_Discount_Tags.xlsx
@@ -326,6 +326,21 @@
         <t>Internal Rule 804 research note: record observed bestseller-sort position, product-page merchant labels, named collection membership, source URLs, check times and uncertainty. Top/featured collection names alone do not prove sales. Preserve as plain text; do not display automatically as customer product description.</t>
       </text>
     </comment>
+    <comment ref="AR1" authorId="0" shapeId="0">
+      <text>
+        <t>website, inferred_description, inferred_product_name, existing, or unverified. Inferred labels are not verified website taxonomy.</t>
+      </text>
+    </comment>
+    <comment ref="AS1" authorId="0" shapeId="0">
+      <text>
+        <t>Exact observed website path or short quote from supplied name/description supporting the inferred product type.</t>
+      </text>
+    </comment>
+    <comment ref="AT1" authorId="0" shapeId="0">
+      <text>
+        <t>ISO-8601 check time; blank when the type remains unverified.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -573,13 +588,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="B2:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -594,7 +608,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -616,7 +629,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -652,7 +664,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -681,7 +692,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -703,7 +713,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -718,7 +727,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -733,7 +741,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -762,7 +769,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="B35" s="2" t="inlineStr">
         <is>
@@ -770,7 +776,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -1893,7 +1898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ1"/>
+  <dimension ref="A1:AT1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1928,6 +1933,9 @@
     <col width="55" customWidth="1" min="31" max="31"/>
     <col width="25" customWidth="1" min="32" max="32"/>
     <col width="80" customWidth="1" min="33" max="33"/>
+    <col width="38" customWidth="1" min="44" max="44"/>
+    <col width="38" customWidth="1" min="45" max="45"/>
+    <col width="38" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2144,6 +2152,21 @@
       <c r="AQ1" s="4" t="inlineStr">
         <is>
           <t>website_category_status</t>
+        </is>
+      </c>
+      <c r="AR1" s="4" t="inlineStr">
+        <is>
+          <t>subcategory_source</t>
+        </is>
+      </c>
+      <c r="AS1" s="4" t="inlineStr">
+        <is>
+          <t>subcategory_evidence</t>
+        </is>
+      </c>
+      <c r="AT1" s="4" t="inlineStr">
+        <is>
+          <t>subcategory_checked_at</t>
         </is>
       </c>
     </row>

--- a/importer-files/Chotu_Products_Import_Template_Discount_Tags.xlsx
+++ b/importer-files/Chotu_Products_Import_Template_Discount_Tags.xlsx
@@ -942,7 +942,7 @@
     <row r="19">
       <c r="A19" s="27" t="inlineStr">
         <is>
-          <t>• category: groups products into tabs in the app, in the order they first appear. subcategory/sku/source_url are kept for reference only.</t>
+          <t>• Category: the single final category label, renamed from the former subcategory column. shop_code is first; confirmed codes repeat on every product and unknown stores stay blank. sku/source_url and subcategory_* evidence fields remain reference/audit data.</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
     <row r="3">
       <c r="A3" s="30" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B3" s="30" t="inlineStr">
@@ -1082,19 +1082,19 @@
       </c>
       <c r="C3" s="30" t="inlineStr">
         <is>
-          <t>Tab/section in the shop</t>
+          <t>Final product category label, formerly exported as subcategory; website evidence first, labelled text inference when missing.</t>
         </is>
       </c>
       <c r="D3" s="30" t="inlineStr">
         <is>
-          <t>Shirts</t>
+          <t>Face Wash</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="30" t="inlineStr">
         <is>
-          <t>subcategory</t>
+          <t>subcategory_source</t>
         </is>
       </c>
       <c r="B4" s="30" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="C4" s="30" t="inlineStr">
         <is>
-          <t>Reference only</t>
+          <t>Audit provenance only: website, inferred_description, inferred_product_name, existing or unverified.</t>
         </is>
       </c>
       <c r="D4" s="30" t="inlineStr">
         <is>
-          <t>Men</t>
+          <t>website</t>
         </is>
       </c>
     </row>
@@ -1901,8 +1901,8 @@
   <dimension ref="A1:AT1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
@@ -1941,17 +1941,17 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
+          <t>shop_code</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
           <t>product_id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>subcategory</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
@@ -2171,9 +2171,9 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A5000">
+  <conditionalFormatting sqref="B2:B5000">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND($A2&lt;&gt;"",COUNTIF($A$2:$A$5000,$A2)&gt;1)</formula>
+      <formula>AND($B2&lt;&gt;"",COUNTIF($B$2:$B$5000,$B2)&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">

--- a/importer-files/Chotu_Products_Import_Template_Discount_Tags.xlsx
+++ b/importer-files/Chotu_Products_Import_Template_Discount_Tags.xlsx
@@ -328,7 +328,7 @@
     </comment>
     <comment ref="AR1" authorId="0" shapeId="0">
       <text>
-        <t>website, inferred_description, inferred_product_name, existing, or unverified. Inferred labels are not verified website taxonomy.</t>
+        <t>website, inferred_description, inferred_product_name, inferred_product_type, manual, existing, or unverified. Public product types are distinct from factual website taxonomy.</t>
       </text>
     </comment>
     <comment ref="AS1" authorId="0" shapeId="0">
@@ -723,7 +723,7 @@
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Products mein nayi row: product_id (unique), category, subcategory, name, description, brand, material, base_price (aur agar discount ho to sale_price), option_groups.</t>
+          <t>Products: shop_code, product_id (unique), Category, name, description, brand, material, base_price, sale_price and option_groups. Category is the supported product type; website path and inference evidence remain separate.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C3" s="30" t="inlineStr">
         <is>
-          <t>Final product category label, formerly exported as subcategory; website evidence first, labelled text inference when missing.</t>
+          <t>Consistent product type from explicit product name and descriptive purpose. Refine broad collection labels; retain original website taxonomy separately. Ignore ingredient and application-tool mentions. Unclear types require review.</t>
         </is>
       </c>
       <c r="D3" s="30" t="inlineStr">

--- a/importer-files/Chotu_Products_Import_Template_Discount_Tags.xlsx
+++ b/importer-files/Chotu_Products_Import_Template_Discount_Tags.xlsx
@@ -2582,7 +2582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2708,6 +2708,21 @@
           <t>source_discount_tag</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>variant_image_status</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>fallback_image_url</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>variant_image_note</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
